--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.51746346946045</v>
+        <v>1.709087813787323</v>
       </c>
       <c r="D2" t="n">
-        <v>49.58735621410086</v>
+        <v>8.05794538479139</v>
       </c>
       <c r="E2" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F2" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.042984632492825</v>
+        <v>1.144485002780084</v>
       </c>
       <c r="D3" t="n">
-        <v>58.60024939910632</v>
+        <v>9.522540527354778</v>
       </c>
       <c r="E3" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F3" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.34067082429092</v>
+        <v>1.842859008947275</v>
       </c>
       <c r="D4" t="n">
-        <v>11.35892098828949</v>
+        <v>1.845824660597043</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F4" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.310014844627</v>
+        <v>3.625377412251888</v>
       </c>
       <c r="D5" t="n">
-        <v>32.49722776575837</v>
+        <v>5.280799511935736</v>
       </c>
       <c r="E5" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F5" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.72098497137386</v>
+        <v>6.292160057848252</v>
       </c>
       <c r="D6" t="n">
-        <v>27.91047506031383</v>
+        <v>4.535452197300997</v>
       </c>
       <c r="E6" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F6" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.994956839885</v>
+        <v>6.986680486481313</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34287619375439</v>
+        <v>6.393217381485088</v>
       </c>
       <c r="E7" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F7" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.21045235839115</v>
+        <v>6.046698508238562</v>
       </c>
       <c r="D8" t="n">
-        <v>17.62023157551094</v>
+        <v>2.863287631020528</v>
       </c>
       <c r="E8" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F8" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.07094218147485</v>
+        <v>7.649028104489663</v>
       </c>
       <c r="D9" t="n">
-        <v>58.10968013301814</v>
+        <v>9.44282302161545</v>
       </c>
       <c r="E9" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F9" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.36745179895472</v>
+        <v>4.609710917330142</v>
       </c>
       <c r="D10" t="n">
-        <v>17.5275132641845</v>
+        <v>2.848220905429981</v>
       </c>
       <c r="E10" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F10" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.31718539192102</v>
+        <v>7.201542626187165</v>
       </c>
       <c r="D11" t="n">
-        <v>44.6487901687002</v>
+        <v>7.255428402413782</v>
       </c>
       <c r="E11" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F11" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.76286837995819</v>
+        <v>4.023966111743206</v>
       </c>
       <c r="D12" t="n">
-        <v>44.91938421134745</v>
+        <v>7.299399934343961</v>
       </c>
       <c r="E12" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F12" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.09673251800123</v>
+        <v>5.703219034175199</v>
       </c>
       <c r="D13" t="n">
-        <v>47.32762438119183</v>
+        <v>7.690738961943673</v>
       </c>
       <c r="E13" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F13" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.23713296715602</v>
+        <v>5.563534107162853</v>
       </c>
       <c r="D14" t="n">
-        <v>54.402917473825</v>
+        <v>8.840474089496563</v>
       </c>
       <c r="E14" t="n">
-        <v>12.94502670877841</v>
+        <v>2.103566840176491</v>
       </c>
       <c r="F14" t="n">
-        <v>15.39680238608341</v>
+        <v>2.501980387738554</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
